--- a/DOSSIES_MULTIFORMATO/CASA_MILITAR/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/CASA_MILITAR/dossie.xlsx
@@ -469,7 +469,11 @@
           <t>cnpj</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>04.312.369/0001-90</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -521,7 +525,11 @@
           <t>faturas_exigiveis</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -529,7 +537,11 @@
           <t>faturas_prescritas</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1236,7 +1248,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2025NE0000490</t>
+          <t>2025NE00490</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1259,14 +1271,14 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Contratação de Serviço licença de sistema de informação, disponibilização de Gestor de Conteúdo WEB - GERWEB, publ de informações, notícias, vídeos e imagens via Website, de acordo com o padrão de com</t>
+          <t>Serviço de Licença de Uso de Sistema de Informação a disponibilização de Gestor de Conteúdo Web. Contrato 003/2025.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2025NE00490</t>
+          <t>2025NE0000490</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1289,7 +1301,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Serviço de Licença de Uso de Sistema de Informação a disponibilização de Gestor de Conteúdo Web. Contrato 003/2025.</t>
+          <t>Contratação de Serviço licença de sistema de informação, disponibilização de Gestor de Conteúdo WEB - GERWEB, publ de informações, notícias, vídeos e imagens via Website, de acordo com o padrão de com</t>
         </is>
       </c>
     </row>
